--- a/reports/demo/demo_orders_corrected.xlsx
+++ b/reports/demo/demo_orders_corrected.xlsx
@@ -30,7 +30,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B183"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,13 +65,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -149,6 +156,12 @@
     <author>IloveCSV</author>
   </authors>
   <commentList>
+    <comment ref="K16" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (regex, open)
+'not-an-email' does not match the pattern ^[\w.+-]+@[\w-]+\.[\w.]+$.</t>
+      </text>
+    </comment>
     <comment ref="E17" authorId="0" shapeId="0">
       <text>
         <t>IloveCSV changed this cell
@@ -156,6 +169,24 @@
 rule: allowed.noncanonical
 method: canonical_category
 approved by: demo-reviewer</t>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (type, open)
+'not a date' is not a date.</t>
+      </text>
+    </comment>
+    <comment ref="D22" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (customer_exists, open)
+'C999' was not found in Customers.customer_id.</t>
+      </text>
+    </comment>
+    <comment ref="A38" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (required, open)
+'order_id' is required but empty.</t>
       </text>
     </comment>
     <comment ref="E52" authorId="0" shapeId="0">
@@ -167,6 +198,24 @@
 approved by: demo-reviewer</t>
       </text>
     </comment>
+    <comment ref="G59" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (range, open)
+5000 is above the maximum 1000.</t>
+      </text>
+    </comment>
+    <comment ref="B62" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (range, open)
+2019-05-01 is below the minimum 2020-01-01.</t>
+      </text>
+    </comment>
+    <comment ref="C75" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (shipped_needs_date, open)
+'ship_date' is required when status == 'Shipped'.</t>
+      </text>
+    </comment>
     <comment ref="E75" authorId="0" shapeId="0">
       <text>
         <t>IloveCSV changed this cell
@@ -176,6 +225,12 @@
 approved by: demo-reviewer</t>
       </text>
     </comment>
+    <comment ref="G92" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (range, open)
+0 is below the minimum 1.</t>
+      </text>
+    </comment>
     <comment ref="G100" authorId="0" shapeId="0">
       <text>
         <t>IloveCSV changed this cell
@@ -183,6 +238,30 @@
 rule: type.stored_as_text
 method: text_to_number
 approved by: demo-reviewer</t>
+      </text>
+    </comment>
+    <comment ref="G121" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (type, open)
+'abc' is not a number.</t>
+      </text>
+    </comment>
+    <comment ref="E131" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (allowed, open)
+'Lost' is not an allowed value for 'status'.</t>
+      </text>
+    </comment>
+    <comment ref="J135" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (total_matches, pending_review)
+Total does not equal quantity x unit price (total=19848.4, quantity=30, unit_price=658.28)</t>
+      </text>
+    </comment>
+    <comment ref="A156" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (regex, open)
+'ORD-12A4' does not match the pattern ^ORD-\d{5}$.</t>
       </text>
     </comment>
     <comment ref="H166" authorId="0" shapeId="0">
@@ -203,6 +282,12 @@
 approved by: demo-reviewer</t>
       </text>
     </comment>
+    <comment ref="B260" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (not_future, open)
+2031-01-01 is in the future.</t>
+      </text>
+    </comment>
     <comment ref="B269" authorId="0" shapeId="0">
       <text>
         <t>IloveCSV changed this cell
@@ -212,9 +297,31 @@
 approved by: demo-reviewer</t>
       </text>
     </comment>
+    <comment ref="C278" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (ship_after_order, open)
+Ship date is before the order date (ship_date=2024-09-21, order_date=2024-09-24)</t>
+      </text>
+    </comment>
+    <comment ref="C282" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (shipped_needs_date, open)
+'ship_date' is required when status == 'Shipped'.</t>
+      </text>
+    </comment>
+    <comment ref="D291" authorId="0" shapeId="0">
+      <text>
+        <t>IloveCSV: UNRESOLVED (required, open)
+'customer_id' is required but empty.</t>
+      </text>
+    </comment>
     <comment ref="A302" authorId="0" shapeId="0">
       <text>
-        <t>IloveCSV: duplicate row approved for removal but kept (workbook contains formulas; deleting rows could break references, so the row was kept and marked).</t>
+        <t>IloveCSV: duplicate row approved for removal but kept (workbook contains formulas; deleting rows could break references, so the row was kept and marked).
+IloveCSV: UNRESOLVED (key.duplicate, open)
+Duplicate key (ORD-00128); first seen in row 129.
+IloveCSV: UNRESOLVED (row.duplicate, open)
+Row repeats row 129 (ignoring order_id; case and spacing ignored).</t>
       </text>
     </comment>
   </commentList>
@@ -1240,7 +1347,7 @@
       <c r="J16" t="n">
         <v>17934.5</v>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>not-an-email</t>
         </is>
@@ -1387,7 +1494,7 @@
           <t>ORD-00019</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>not a date</t>
         </is>
@@ -1479,7 +1586,7 @@
       <c r="B22" s="1" t="n">
         <v>45691</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>C999</t>
         </is>
@@ -2173,6 +2280,7 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" s="6" t="n"/>
       <c r="B38" s="1" t="n">
         <v>45755</v>
       </c>
@@ -3124,7 +3232,7 @@
           <t>Web</t>
         </is>
       </c>
-      <c r="G59" t="n">
+      <c r="G59" s="6" t="n">
         <v>5000</v>
       </c>
       <c r="H59" t="n">
@@ -3235,7 +3343,7 @@
           <t>ORD-00061</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="7" t="n">
         <v>43586</v>
       </c>
       <c r="C62" s="1" t="n">
@@ -3814,6 +3922,7 @@
       <c r="B75" s="1" t="n">
         <v>45608</v>
       </c>
+      <c r="C75" s="6" t="n"/>
       <c r="D75" t="inlineStr">
         <is>
           <t>C028</t>
@@ -4579,7 +4688,7 @@
           <t>Store</t>
         </is>
       </c>
-      <c r="G92" t="n">
+      <c r="G92" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H92" t="n">
@@ -5863,7 +5972,7 @@
           <t>Web</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="G121" s="6" t="inlineStr">
         <is>
           <t>abc</t>
         </is>
@@ -6299,7 +6408,7 @@
           <t>C039</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
+      <c r="E131" s="6" t="inlineStr">
         <is>
           <t>Lost</t>
         </is>
@@ -6498,7 +6607,7 @@
       <c r="I135" t="n">
         <v>110.39</v>
       </c>
-      <c r="J135" t="n">
+      <c r="J135" s="6" t="n">
         <v>19848.4</v>
       </c>
       <c r="K135" t="inlineStr">
@@ -7402,7 +7511,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
+      <c r="A156" s="6" t="inlineStr">
         <is>
           <t>ORD-12A4</t>
         </is>
@@ -12006,7 +12115,7 @@
           <t>ORD-00259</t>
         </is>
       </c>
-      <c r="B260" s="1" t="n">
+      <c r="B260" s="7" t="n">
         <v>47849</v>
       </c>
       <c r="D260" t="inlineStr">
@@ -12807,7 +12916,7 @@
       <c r="B278" s="1" t="n">
         <v>45559</v>
       </c>
-      <c r="C278" s="1" t="n">
+      <c r="C278" s="7" t="n">
         <v>45556</v>
       </c>
       <c r="D278" t="inlineStr">
@@ -12981,6 +13090,7 @@
       <c r="B282" s="1" t="n">
         <v>45302</v>
       </c>
+      <c r="C282" s="6" t="n"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>C037</t>
@@ -13377,6 +13487,7 @@
       <c r="C291" s="1" t="n">
         <v>45648</v>
       </c>
+      <c r="D291" s="6" t="n"/>
       <c r="E291" t="inlineStr">
         <is>
           <t>Delivered</t>
@@ -13847,7 +13958,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="4" t="inlineStr">
+      <c r="A302" s="6" t="inlineStr">
         <is>
           <t>ORD-00128</t>
         </is>
